--- a/ig/mc-add-link-doc/StructureDefinition-as-ext-device-number-authorization-arhgos.xlsx
+++ b/ig/mc-add-link-doc/StructureDefinition-as-ext-device-number-authorization-arhgos.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:30:52+00:00</t>
+    <t>2023-05-17T07:53:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -253,7 +253,7 @@
     <t>Identifiant fonctionnel de l'autorisation ARHGOS de l'EML.</t>
   </si>
   <si>
-    <t>Synonyme MOS : numeroAutorisationARHGOS</t>
+    <t>Synonyme : numeroAutorisationARHGOS</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
